--- a/光伏配储项目/电价数据/2026/春城站.xlsx
+++ b/光伏配储项目/电价数据/2026/春城站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7095399999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51771</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26147</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.22022</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26215</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07956999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06570999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05540999999999999</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03577</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05763</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03853</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04708</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01444</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01791</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08604000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21284</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18589</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.12209</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01108</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.009820000000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.12003</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11855</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.17915</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.18067</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.15307</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12561</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19777</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.01733</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24697</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5292100000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.74391</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61139</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.5279199999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.08259999999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5860599999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5619500000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48013</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42261</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62951</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.4316</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74541</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.02617</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7987300000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5366599999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52395</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50663</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50761</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50215</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51651</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6288899999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7196699999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09478</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.03595</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26773</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2800299999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61499</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.59096</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27292</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.24218</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.24809</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25102</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26007</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.47022</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68777</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7930499999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78706</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80371</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7842899999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.58928</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43284</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33356</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5149600000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46504</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47399</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44806</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.14388</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25347</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.25364</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22219</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15864</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24338</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.03724</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48589</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.03920000000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50863</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34338</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.22242</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13821</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.13434</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.09843</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26755</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.46059</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.22155</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.03393</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.03866</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06583</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.21515</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.06128</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.09029000000000001</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.12233</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19546</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22376</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23264</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16232</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23699</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25274</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29095</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04534000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04663</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04175</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04602000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04583</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22033</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14645</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03686</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66355</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03194</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04139</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10653</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04223</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04441</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04133</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03985</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04188</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04051</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04676</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20145</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33697</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32074</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15985</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17241</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14891</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16064</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15994</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23835</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21536</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92302</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8920399999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31106</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63609</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21405</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88198</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56528</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35858</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05191</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81477</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79688</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7965099999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87971</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88636</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5155</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4286</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47546</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2357</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87966</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55152</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5454199999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50588</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58866</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59661</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65626</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40734</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5605599999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86187</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.65022</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8118500000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84912</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9858899999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6102000000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16456</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20052</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43206</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44779</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35032</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1406</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7071900000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79991</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65234</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5875499999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.54475</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.05894</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6367200000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04461</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6524800000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26524</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58572</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7164400000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43866</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32566</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14721</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15406</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14437</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14075</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14413</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14257</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14467</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1421</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03374</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11413</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14146</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14663</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44111</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44042</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35006</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5485599999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46973</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27265</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24727</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24264</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18461</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.27054</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26484</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24362</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36054</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03702</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25276</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20112</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07173</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18121</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46878</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73349</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30101</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5994700000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.88946</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48625</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13451</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02248</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11223</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02235</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23079</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14434</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.21012</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.2835299999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68745</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6469</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6423099999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.66918</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49161</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.85511</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47427</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.50414</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.48681</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4799</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42157</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45786</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.58124</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.51448</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12792</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00332</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.008449999999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.12437</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08679000000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.03595</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00358</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42515</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5229600000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5250199999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6071299999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7431599999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.74173</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.71915</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80948</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.57384</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5402100000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8784999999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8059400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63819</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69386</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.49583</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.49108</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48438</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5601699999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46818</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43271</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45705</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40391</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15633</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04425</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18346</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36407</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23435</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13329</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23352</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16004</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25613</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00392</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14525</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15363</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03051</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21791</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23047</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.15429</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26519</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35227</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22738</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21743</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18043</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.08774999999999999</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00147</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04246</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.06631999999999999</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03302</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04144</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04819</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.17007</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21515</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27727</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24673</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26705</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25155</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17965</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05727</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06651</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14616</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26184</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20684</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21414</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17053</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19072</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22047</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24474</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26176</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24705</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18474</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06619</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50178</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.55175</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.07959999999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.23145</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.01732</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20316</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09473999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04422</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05754</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20854</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03375</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02818</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13155</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03834000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04212</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02769</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.03059</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25677</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3253</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11386</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.26358</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.25396</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11517</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16745</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.15087</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07401000000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33119</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.51427</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.18245</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26337</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2800299999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25984</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24043</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48967</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47993</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.09381</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47555</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.73964</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45949</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46965</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.16206</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.27354</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17603</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56284</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49937</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77435</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55313</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27694</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21103</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23542</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.17126</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.00993</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14333</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01888</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.01551</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.15901</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.03826</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.00975</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04028</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02311</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23448</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04008</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03384</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02691</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.03214</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12331</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.08229</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.13441</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.16909</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.20447</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.25214</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19208</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37851</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8156599999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.22899</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.09112000000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01459</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01411</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01298</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03336</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.12344</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03215999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00704</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04367</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15445</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03696</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.18101</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13728</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.16156</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.21292</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.20418</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.23001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.25447</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.51689</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41702</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38581</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52396</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19936</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12691</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17642</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20041</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19536</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09762999999999999</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.06104</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07894</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04333</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04353</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06927</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02931</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.14087</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.15824</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10206</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20969</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18289</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10406</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04720000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23769</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11832</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10135</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20894</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.19442</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20206</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17341</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23825</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40734</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49614</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38418</v>
       </c>
     </row>
   </sheetData>
